--- a/app/src/main/java/com/example/methodmesh/modules/surveying/docs/example_odk_survey_traverse.xlsx
+++ b/app/src/main/java/com/example/methodmesh/modules/surveying/docs/example_odk_survey_traverse.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R662cc75ac7d04ce2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R9856082b62b74dd9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R27437118dd684786"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Ra4474836d4b34582"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rb8ab8a277cd1442b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R9459ad1c38244e84"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -27,7 +27,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -39,6 +39,11 @@
         <x:fgColor rgb="FF244C5A"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2E8F0"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -47,7 +52,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -72,6 +77,8 @@
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -835,28 +842,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="9" t="str">
+      <x:c r="A1" s="13" t="str">
         <x:v>form_title</x:v>
       </x:c>
-      <x:c r="B1" s="9" t="str">
+      <x:c r="B1" s="13" t="str">
         <x:v>form_id</x:v>
       </x:c>
-      <x:c r="C1" s="9" t="str">
+      <x:c r="C1" s="13" t="str">
         <x:v>version</x:v>
       </x:c>
-      <x:c r="D1" s="9" t="str">
+      <x:c r="D1" s="13" t="str">
         <x:v>instance_name</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
-        <x:v>survey.traverse</x:v>
+        <x:v>Survey Traverse</x:v>
       </x:c>
       <x:c r="B2" t="str">
         <x:v>survey_traverse</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>20260904</x:v>
+        <x:v>2026090703</x:v>
       </x:c>
       <x:c r="D2" t="str">
         <x:v>survey.traverse</x:v>
